--- a/Assets/ConfigTables/Data/Narrative.xlsx
+++ b/Assets/ConfigTables/Data/Narrative.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Object" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bar" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trigger" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EventDate" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Result" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Condition" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Template" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SetupParams" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choice" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Object" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Bar" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Trigger" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Event" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="EventDate" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Result" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Condition" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Template" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="SetupParams" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Choice" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2875,7 +2875,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:O22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2892,1142 +2892,1203 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>##var</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>eventId</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>eventKind</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>actorId</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>targetId</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>titleText</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>contentKey</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>setupType</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>setupKey</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>onceOnly</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>logTag</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>presentationClass</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>presentationKey</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>presentationLogTag</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>eventProperty</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>##type</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="I2" s="1" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr">
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t>bool</t>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>string</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>##group</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>##</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>eventId</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>eventKind</t>
         </is>
       </c>
-      <c r="D4" s="1" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>actorId</t>
         </is>
       </c>
-      <c r="E4" s="1" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>targetId</t>
         </is>
       </c>
-      <c r="F4" s="1" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>titleText</t>
         </is>
       </c>
-      <c r="G4" s="1" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>contentKey</t>
         </is>
       </c>
-      <c r="H4" s="1" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>setupType</t>
         </is>
       </c>
-      <c r="I4" s="1" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>setupKey</t>
         </is>
       </c>
-      <c r="J4" s="1" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>onceOnly</t>
         </is>
       </c>
-      <c r="K4" s="1" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>logTag</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>presentationClass</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>presentationKey</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>presentationLogTag</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>eventProperty</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n"/>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>EV_ACT_MEET</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>actor</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>player</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>npc_b</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>ev.act.meet.title</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>ev.act.meet.p1|ev.act.meet.p2</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Tpl_WorldBroadcast</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>act_meet</t>
         </is>
       </c>
-      <c r="J5" s="2" t="b">
+      <c r="J5" t="b">
         <v>0</v>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>ACT_MEET</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n"/>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>EV_ACT_C_WITH_B</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>actor</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>player</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>npc_c</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>ev.act.cwithb.title</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>ev.act.cwithb.p1|ev.act.cwithb.p2</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>Tpl_WorldBroadcast</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>act_cwithb</t>
         </is>
       </c>
-      <c r="J6" s="2" t="b">
+      <c r="J6" t="b">
         <v>0</v>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>ACT_CWITHB</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n"/>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>EV_ACT_SALON</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>actor</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>player</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>npc_a</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>ev.act.salon.title</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>ev.act.salon.p1|ev.act.salon.p2</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>Tpl_WorldBroadcast</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>act_salon</t>
         </is>
       </c>
-      <c r="J7" s="2" t="b">
+      <c r="J7" t="b">
         <v>0</v>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>ACT_SALON</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n"/>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>EV_ACT_C_PEER</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>actor</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>player</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>npc_c</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>ev.act.peer.title</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>ev.act.peer.p1|ev.act.peer.p2</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>Tpl_WorldBroadcast</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>act_peer</t>
         </is>
       </c>
-      <c r="J8" s="2" t="b">
+      <c r="J8" t="b">
         <v>0</v>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>ACT_PEER</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n"/>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>EV_TALK_CAFE</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>actor</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>player</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>npc_b</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>ev.talk.cafe.title</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>ev.talk.cafe.p1</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>Tpl_TwoPersonTalk</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>talk_cafe</t>
         </is>
       </c>
-      <c r="J9" s="2" t="b">
+      <c r="J9" t="b">
         <v>0</v>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>TALK_CAFE</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n"/>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>EV_AB_SWEAR</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>actor</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>npc_a</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>npc_b</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>ev.ab.swear.title</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>ev.ab.swear.p1|ev.ab.swear.p2|ev.ab.swear.p3</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>Tpl_TwoPersonTalk</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>ab_swear</t>
         </is>
       </c>
-      <c r="J10" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>AB_SWEAR</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n"/>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>EV_BC_SWEAR</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>actor</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>npc_c</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>npc_b</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>ev.bc.swear.title</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>ev.bc.swear.p1|ev.bc.swear.p2|ev.bc.swear.p3</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Tpl_TwoPersonTalk</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>bc_swear</t>
         </is>
       </c>
-      <c r="J11" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>BC_SWEAR</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n"/>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>EV_STANDOFF</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>actor</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>npc_c</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>npc_a</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>ev.standoff.title</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>ev.standoff.p1|ev.standoff.p2|ev.standoff.p3</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>Tpl_TwoPersonTalk</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>standoff</t>
         </is>
       </c>
-      <c r="J12" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>STANDOFF</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n"/>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>EV_COMRADE</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>actor</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>npc_a</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>npc_c</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>ev.comrade.title</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>ev.comrade.p1|ev.comrade.p2</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>Tpl_TwoPersonTalk</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>comrade</t>
         </is>
       </c>
-      <c r="J13" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>COM_RADE</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n"/>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>EV_PRISON</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>world</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>world</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>npc_b</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>ev.prison.title</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>ev.prison.p1|ev.prison.p2</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>Tpl_WorldBroadcast</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>prison</t>
         </is>
       </c>
-      <c r="J14" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="inlineStr">
         <is>
           <t>PRISON</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n"/>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>EV_RESCUE</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>actor</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>player</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>npc_b</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>ev.rescue.title</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>ev.rescue.p1|ev.rescue.p2</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>Tpl_TwoPersonTalk</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>rescue</t>
         </is>
       </c>
-      <c r="J15" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="J15" t="b">
+        <v>1</v>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>RESCUE</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n"/>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>EV_D_QUARREL_1</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>actor</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>npc_d</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>npc_b</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>ev.dq1.title</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>ev.dq1.p1|ev.dq1.p2</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>Tpl_TwoPersonTalk</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>dq1</t>
         </is>
       </c>
-      <c r="J16" s="2" t="b">
+      <c r="J16" t="b">
         <v>0</v>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>DQ_1</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n"/>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>EV_D_QUARREL_2</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>actor</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>npc_d</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>npc_b</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>ev.dq2.title</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>ev.dq2.p1|ev.dq2.p2</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>Tpl_TwoPersonTalk</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>dq2</t>
         </is>
       </c>
-      <c r="J17" s="2" t="b">
+      <c r="J17" t="b">
         <v>0</v>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>DQ_2</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n"/>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>EV_D_QUARREL_N</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>actor</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>npc_d</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>npc_b</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>ev.dqn.title</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>ev.dqn.p1</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>Tpl_MonoTalk</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>dqn</t>
         </is>
       </c>
-      <c r="J18" s="2" t="b">
+      <c r="J18" t="b">
         <v>0</v>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>DQ_N</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n"/>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>EV_ELOPE</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>actor</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>npc_b</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>npc_a</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>ev.elope.title</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>ev.elope.p1|ev.elope.p2</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>Tpl_TwoPersonTalk</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>elope</t>
         </is>
       </c>
-      <c r="J19" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="J19" t="b">
+        <v>1</v>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>ELOPE</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n"/>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>EV_FLEE</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>world</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>world</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>npc_b</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>ev.flee.title</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>ev.flee.p1|ev.flee.p2</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>Tpl_WorldBroadcast</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>flee</t>
         </is>
       </c>
-      <c r="J20" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="J20" t="b">
+        <v>1</v>
+      </c>
+      <c r="K20" t="inlineStr">
         <is>
           <t>FLEE</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n"/>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>EV_REVOLUTION</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>world</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>world</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr"/>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>ev.rev.title</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>ev.rev.p1|ev.rev.p2|ev.rev.p3</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>Tpl_CutScene</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>revolution</t>
         </is>
       </c>
-      <c r="J21" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="J21" t="b">
+        <v>1</v>
+      </c>
+      <c r="K21" t="inlineStr">
         <is>
           <t>REVOLUTION</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n"/>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>EV_MUSICIAN</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>world</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>world</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>npc_b</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>ev.musician.title</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>ev.musician.p1|ev.musician.p2</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>Tpl_WorldBroadcast</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>musician</t>
         </is>
       </c>
-      <c r="J22" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="J22" t="b">
+        <v>1</v>
+      </c>
+      <c r="K22" t="inlineStr">
         <is>
           <t>MUSICIAN</t>
         </is>
